--- a/MedicalClinics.xlsx
+++ b/MedicalClinics.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hgreatrex/Documents/GitHub/Teaching/GEOG-364/Geog364-2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E84964DC-13F8-A547-AD81-8EED766AACE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E899408-E531-1F4F-96A1-CA3CC3776735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="15440" xr2:uid="{E43EC704-E86A-234A-95F9-026FCD5E8DF0}"/>
+    <workbookView xWindow="15260" yWindow="500" windowWidth="14260" windowHeight="15440" xr2:uid="{E43EC704-E86A-234A-95F9-026FCD5E8DF0}"/>
   </bookViews>
   <sheets>
     <sheet name="medical clinics" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'medical clinics'!$B$1:$B$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'medical clinics'!$D$1:$D$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
   <si>
     <t>Madison Parish Hospital</t>
   </si>
@@ -83,9 +83,6 @@
     <t>Delta Regional Health Clinic</t>
   </si>
   <si>
-    <t>United Medical Inc</t>
-  </si>
-  <si>
     <t>Jackson Rural Health Clinic</t>
   </si>
   <si>
@@ -108,6 +105,9 @@
   </si>
   <si>
     <t>latitudE</t>
+  </si>
+  <si>
+    <t>NumberDoctors</t>
   </si>
 </sst>
 </file>
@@ -976,283 +976,324 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01736A12-39A0-FC44-A36A-3B3F1387DBBE}">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2">
+        <v>20</v>
+      </c>
+      <c r="D2">
+        <v>32.403619800000001</v>
+      </c>
+      <c r="E2">
+        <v>-91.184966399999993</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3">
+        <v>25</v>
+      </c>
+      <c r="D3">
+        <v>32.868368099999998</v>
+      </c>
+      <c r="E3">
+        <v>-91.382387899999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4">
+        <v>18</v>
+      </c>
+      <c r="D4">
+        <v>33.306414799999999</v>
+      </c>
+      <c r="E4">
+        <v>-91.2903886</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5">
+        <v>96</v>
+      </c>
+      <c r="D5">
+        <v>32.5813311</v>
+      </c>
+      <c r="E5">
+        <v>-90.083076800000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6">
+        <v>163</v>
+      </c>
+      <c r="D6">
+        <v>32.374493299999997</v>
+      </c>
+      <c r="E6">
+        <v>-90.824793599999893</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7">
         <v>23</v>
       </c>
-      <c r="C1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>-91.184966399999993</v>
-      </c>
-      <c r="B2">
-        <v>32.403619800000001</v>
-      </c>
-      <c r="C2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="D7">
+        <v>33.4576013</v>
+      </c>
+      <c r="E7">
+        <v>-90.6495666</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>32.900163200000001</v>
+      </c>
+      <c r="E8">
+        <v>-90.875071199999994</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>-91.382387899999998</v>
-      </c>
-      <c r="B3">
-        <v>32.868368099999998</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C9">
+        <v>5</v>
+      </c>
+      <c r="D9">
+        <v>33.381512000000001</v>
+      </c>
+      <c r="E9">
+        <v>-91.039733099999907</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>-91.2903886</v>
-      </c>
-      <c r="B4">
-        <v>33.306414799999999</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="C10">
+        <v>5</v>
+      </c>
+      <c r="D10">
+        <v>32.861331900000003</v>
+      </c>
+      <c r="E10">
+        <v>-91.381385799999904</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+      <c r="D11">
+        <v>32.858945900000002</v>
+      </c>
+      <c r="E11">
+        <v>-90.4043432</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12">
+        <v>5</v>
+      </c>
+      <c r="D12">
+        <v>32.322080300000003</v>
+      </c>
+      <c r="E12">
+        <v>-90.865793599999904</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13">
         <v>2</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D13">
+        <v>32.905795099999999</v>
+      </c>
+      <c r="E13">
+        <v>-90.884939000000003</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5">
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <v>32.809706499999997</v>
+      </c>
+      <c r="E14">
+        <v>-91.171239499999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15">
+        <v>5</v>
+      </c>
+      <c r="D15">
+        <v>33.353937500000001</v>
+      </c>
+      <c r="E15">
+        <v>-91.042079999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16">
+        <v>32</v>
+      </c>
+      <c r="D16">
+        <v>33.404327600000002</v>
+      </c>
+      <c r="E16">
+        <v>-91.051145599999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17">
+        <v>4</v>
+      </c>
+      <c r="D17">
+        <v>32.905056799999997</v>
+      </c>
+      <c r="E17">
+        <v>-90.884736199999907</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18">
+        <v>57</v>
+      </c>
+      <c r="D18">
+        <v>32.774979000000002</v>
+      </c>
+      <c r="E18">
         <v>-91.917384599999906</v>
       </c>
-      <c r="B5">
-        <v>32.774979000000002</v>
-      </c>
-      <c r="C5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>-90.824793599999893</v>
-      </c>
-      <c r="B6">
-        <v>32.374493299999997</v>
-      </c>
-      <c r="C6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>-90.6495666</v>
-      </c>
-      <c r="B7">
-        <v>33.4576013</v>
-      </c>
-      <c r="C7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>-90.875071199999994</v>
-      </c>
-      <c r="B8">
-        <v>32.900163200000001</v>
-      </c>
-      <c r="C8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>-91.039733099999907</v>
-      </c>
-      <c r="B9">
-        <v>33.381512000000001</v>
-      </c>
-      <c r="C9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>-91.381385799999904</v>
-      </c>
-      <c r="B10">
-        <v>32.861331900000003</v>
-      </c>
-      <c r="C10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>-90.4043432</v>
-      </c>
-      <c r="B11">
-        <v>32.858945900000002</v>
-      </c>
-      <c r="C11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>-90.083076800000001</v>
-      </c>
-      <c r="B12">
-        <v>32.5813311</v>
-      </c>
-      <c r="C12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>-90.865793599999904</v>
-      </c>
-      <c r="B13">
-        <v>32.322080300000003</v>
-      </c>
-      <c r="C13" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>-90.884939000000003</v>
-      </c>
-      <c r="B14">
-        <v>32.905795099999999</v>
-      </c>
-      <c r="C14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>-91.171239499999999</v>
-      </c>
-      <c r="B15">
-        <v>32.809706499999997</v>
-      </c>
-      <c r="C15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>-91.042079999999999</v>
-      </c>
-      <c r="B16">
-        <v>33.353937500000001</v>
-      </c>
-      <c r="C16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>-91.051145599999998</v>
-      </c>
-      <c r="B17">
-        <v>33.404327600000002</v>
-      </c>
-      <c r="C17" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>-91.041099699999904</v>
-      </c>
-      <c r="B18">
-        <v>33.3576853</v>
-      </c>
-      <c r="C18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>-90.884736199999907</v>
-      </c>
-      <c r="B19">
-        <v>32.905056799999997</v>
-      </c>
-      <c r="C19" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" t="s">
-        <v>18</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:B19" xr:uid="{01736A12-39A0-FC44-A36A-3B3F1387DBBE}"/>
+  <autoFilter ref="D1:D17" xr:uid="{01736A12-39A0-FC44-A36A-3B3F1387DBBE}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>